--- a/src/test/java/fr/autom13/Inscription/excel/membres.xlsx
+++ b/src/test/java/fr/autom13/Inscription/excel/membres.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Formation\Documents\ProjectAutom1\src\test\java\fr\autom13\Inscription\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C284E8-CEF0-4F71-838A-3EAC42A8F6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA7361E-17AF-4F4E-AC59-16787F0FA54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1008" yWindow="696" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -139,12 +139,6 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Masculin</t>
-  </si>
-  <si>
-    <t>Féminin</t>
-  </si>
-  <si>
     <t>birthdate</t>
   </si>
   <si>
@@ -169,19 +163,25 @@
     <t>skill</t>
   </si>
   <si>
-    <t>Jardenieer</t>
-  </si>
-  <si>
-    <t>Propriétaire</t>
-  </si>
-  <si>
-    <t>Expert</t>
-  </si>
-  <si>
-    <t>Débutant</t>
-  </si>
-  <si>
-    <t>Confirmé</t>
+    <t>EXPERT</t>
+  </si>
+  <si>
+    <t>CONFIRMED</t>
+  </si>
+  <si>
+    <t>BEGINNER</t>
+  </si>
+  <si>
+    <t>JARDEENER</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>FEMALE</t>
   </si>
 </sst>
 </file>
@@ -586,28 +586,28 @@
         <v>38</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -624,7 +624,7 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -645,10 +645,10 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -665,7 +665,7 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -686,10 +686,10 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -706,7 +706,7 @@
         <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
@@ -727,10 +727,10 @@
         <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -747,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>22</v>
@@ -768,10 +768,10 @@
         <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -788,7 +788,7 @@
         <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>22</v>
@@ -809,10 +809,10 @@
         <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/fr/autom13/Inscription/excel/membres.xlsx
+++ b/src/test/java/fr/autom13/Inscription/excel/membres.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Formation\Documents\ProjectAutom1\src\test\java\fr\autom13\Inscription\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA7361E-17AF-4F4E-AC59-16787F0FA54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993D2488-BD8D-4728-938A-CC0BA04DCFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1008" yWindow="696" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
